--- a/artfynd/A 56625-2024 artfynd.xlsx
+++ b/artfynd/A 56625-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152375</v>
+        <v>121152342</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554321</v>
+        <v>554412</v>
       </c>
       <c r="R2" t="n">
-        <v>6705090</v>
+        <v>6704920</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152342</v>
+        <v>121152341</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554412</v>
+        <v>554375</v>
       </c>
       <c r="R3" t="n">
-        <v>6704920</v>
+        <v>6704890</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
         <v>121152337</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152311</v>
+        <v>121152375</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554196</v>
+        <v>554321</v>
       </c>
       <c r="R5" t="n">
         <v>6705090</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152341</v>
+        <v>121152373</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554375</v>
+        <v>554322</v>
       </c>
       <c r="R6" t="n">
-        <v>6704890</v>
+        <v>6705100</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152279</v>
+        <v>121152372</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554309</v>
+        <v>554115</v>
       </c>
       <c r="R7" t="n">
-        <v>6705080</v>
+        <v>6705000</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152336</v>
+        <v>121152311</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553971</v>
+        <v>554196</v>
       </c>
       <c r="R8" t="n">
-        <v>6704870</v>
+        <v>6705090</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152373</v>
+        <v>121152336</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554322</v>
+        <v>553971</v>
       </c>
       <c r="R9" t="n">
-        <v>6705100</v>
+        <v>6704870</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152280</v>
+        <v>121152279</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554310</v>
+        <v>554309</v>
       </c>
       <c r="R10" t="n">
-        <v>6705060</v>
+        <v>6705080</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152372</v>
+        <v>121152280</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554115</v>
+        <v>554310</v>
       </c>
       <c r="R11" t="n">
-        <v>6705000</v>
+        <v>6705060</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 56625-2024 artfynd.xlsx
+++ b/artfynd/A 56625-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121152342</v>
+        <v>121152311</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554412</v>
+        <v>554196</v>
       </c>
       <c r="R2" t="n">
-        <v>6704920</v>
+        <v>6705090</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152341</v>
+        <v>121152373</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554375</v>
+        <v>554322</v>
       </c>
       <c r="R3" t="n">
-        <v>6704890</v>
+        <v>6705100</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152337</v>
+        <v>121152372</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553997</v>
+        <v>554115</v>
       </c>
       <c r="R4" t="n">
-        <v>6704900</v>
+        <v>6705000</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152375</v>
+        <v>121152337</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554321</v>
+        <v>553997</v>
       </c>
       <c r="R5" t="n">
-        <v>6705090</v>
+        <v>6704900</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152373</v>
+        <v>121152336</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554322</v>
+        <v>553971</v>
       </c>
       <c r="R6" t="n">
-        <v>6705100</v>
+        <v>6704870</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152372</v>
+        <v>121152341</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554115</v>
+        <v>554375</v>
       </c>
       <c r="R7" t="n">
-        <v>6705000</v>
+        <v>6704890</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152311</v>
+        <v>121152279</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554196</v>
+        <v>554309</v>
       </c>
       <c r="R8" t="n">
-        <v>6705090</v>
+        <v>6705080</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152336</v>
+        <v>121152342</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553971</v>
+        <v>554412</v>
       </c>
       <c r="R9" t="n">
-        <v>6704870</v>
+        <v>6704920</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152279</v>
+        <v>121152375</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554309</v>
+        <v>554321</v>
       </c>
       <c r="R10" t="n">
-        <v>6705080</v>
+        <v>6705090</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>121152280</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 56625-2024 artfynd.xlsx
+++ b/artfynd/A 56625-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121152311</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152373</v>
+        <v>121152372</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554322</v>
+        <v>554115</v>
       </c>
       <c r="R3" t="n">
-        <v>6705100</v>
+        <v>6705000</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152372</v>
+        <v>121152279</v>
       </c>
       <c r="B4" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554115</v>
+        <v>554309</v>
       </c>
       <c r="R4" t="n">
-        <v>6705000</v>
+        <v>6705080</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,7 +1011,7 @@
         <v>121152337</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152336</v>
+        <v>121152375</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553971</v>
+        <v>554321</v>
       </c>
       <c r="R6" t="n">
-        <v>6704870</v>
+        <v>6705090</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1233,7 +1233,7 @@
         <v>121152341</v>
       </c>
       <c r="B7" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152279</v>
+        <v>121152280</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554309</v>
+        <v>554310</v>
       </c>
       <c r="R8" t="n">
-        <v>6705080</v>
+        <v>6705060</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152342</v>
+        <v>121152336</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554412</v>
+        <v>553971</v>
       </c>
       <c r="R9" t="n">
-        <v>6704920</v>
+        <v>6704870</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152375</v>
+        <v>121152342</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554321</v>
+        <v>554412</v>
       </c>
       <c r="R10" t="n">
-        <v>6705090</v>
+        <v>6704920</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152280</v>
+        <v>121152373</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554310</v>
+        <v>554322</v>
       </c>
       <c r="R11" t="n">
-        <v>6705060</v>
+        <v>6705100</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 56625-2024 artfynd.xlsx
+++ b/artfynd/A 56625-2024 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152372</v>
+        <v>121152341</v>
       </c>
       <c r="B3" t="n">
         <v>91989</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554115</v>
+        <v>554375</v>
       </c>
       <c r="R3" t="n">
-        <v>6705000</v>
+        <v>6704890</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121152279</v>
+        <v>121152342</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554309</v>
+        <v>554412</v>
       </c>
       <c r="R4" t="n">
-        <v>6705080</v>
+        <v>6704920</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152337</v>
+        <v>121152372</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553997</v>
+        <v>554115</v>
       </c>
       <c r="R5" t="n">
-        <v>6704900</v>
+        <v>6705000</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152375</v>
+        <v>121152279</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554321</v>
+        <v>554309</v>
       </c>
       <c r="R6" t="n">
-        <v>6705090</v>
+        <v>6705080</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152341</v>
+        <v>121152373</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554375</v>
+        <v>554322</v>
       </c>
       <c r="R7" t="n">
-        <v>6704890</v>
+        <v>6705100</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121152280</v>
+        <v>121152337</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554310</v>
+        <v>553997</v>
       </c>
       <c r="R8" t="n">
-        <v>6705060</v>
+        <v>6704900</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121152336</v>
+        <v>121152375</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553971</v>
+        <v>554321</v>
       </c>
       <c r="R9" t="n">
-        <v>6704870</v>
+        <v>6705090</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121152342</v>
+        <v>121152280</v>
       </c>
       <c r="B10" t="n">
         <v>98098</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554412</v>
+        <v>554310</v>
       </c>
       <c r="R10" t="n">
-        <v>6704920</v>
+        <v>6705060</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121152373</v>
+        <v>121152336</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554322</v>
+        <v>553971</v>
       </c>
       <c r="R11" t="n">
-        <v>6705100</v>
+        <v>6704870</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 56625-2024 artfynd.xlsx
+++ b/artfynd/A 56625-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121152372</v>
+        <v>121152279</v>
       </c>
       <c r="B5" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554115</v>
+        <v>554309</v>
       </c>
       <c r="R5" t="n">
-        <v>6705000</v>
+        <v>6705080</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152279</v>
+        <v>121152373</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554309</v>
+        <v>554322</v>
       </c>
       <c r="R6" t="n">
-        <v>6705080</v>
+        <v>6705100</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152373</v>
+        <v>121152372</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554322</v>
+        <v>554115</v>
       </c>
       <c r="R7" t="n">
-        <v>6705100</v>
+        <v>6705000</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
